--- a/public/exports-from-60/32264328.xlsx
+++ b/public/exports-from-60/32264328.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221240</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221240</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221240</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">

--- a/public/exports-from-60/32264328.xlsx
+++ b/public/exports-from-60/32264328.xlsx
@@ -116,7 +116,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alrøvej 357</t>
+          <t xml:space="preserve">Havnegade 4B</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -126,16 +126,16 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4191418</t>
+          <t xml:space="preserve">4194186</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J2">
-        <v>417</v>
+        <v>266</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -191,7 +191,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 4B</t>
+          <t xml:space="preserve">Havnegade 4C</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -206,11 +206,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J3">
-        <v>266</v>
+        <v>151</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -266,7 +266,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 4C</t>
+          <t xml:space="preserve">Havnegade 4E</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -281,11 +281,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J4">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 4E</t>
+          <t xml:space="preserve">Holsteinsgade 14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -351,16 +351,16 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194186</t>
+          <t xml:space="preserve">4197138</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J5">
-        <v>142</v>
+        <v>64</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -416,7 +416,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holsteinsgade 14</t>
+          <t xml:space="preserve">Højmarkvej 10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -426,16 +426,16 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197138</t>
+          <t xml:space="preserve">4197392</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J6">
-        <v>64</v>
+        <v>257</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -501,16 +501,16 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197392</t>
+          <t xml:space="preserve">4197393</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J7">
-        <v>257</v>
+        <v>103</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -566,26 +566,26 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarkvej 10</t>
+          <t xml:space="preserve">Landevejen 30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197393</t>
+          <t xml:space="preserve">4194793</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J8">
-        <v>103</v>
+        <v>1607</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -641,17 +641,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landevejen 30</t>
+          <t xml:space="preserve">Møllevej 3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194793</t>
+          <t xml:space="preserve">4199010</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="J9">
-        <v>1607</v>
+        <v>78</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -726,16 +726,16 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199010</t>
+          <t xml:space="preserve">4199045</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J10">
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 3</t>
+          <t xml:space="preserve">Nølevvej 6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -801,16 +801,16 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199045</t>
+          <t xml:space="preserve">7349415</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J11">
-        <v>500</v>
+        <v>3084</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nølevvej 6</t>
+          <t xml:space="preserve">Nølevvej 8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -881,11 +881,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J12">
-        <v>3084</v>
+        <v>134</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nølevvej 8</t>
+          <t xml:space="preserve">Rosensgade 59</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -951,16 +951,16 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7349415</t>
+          <t xml:space="preserve">8567252</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J13">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosensgade 59</t>
+          <t xml:space="preserve">Rude Havvej 21B</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1026,16 +1026,16 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">8567252</t>
+          <t xml:space="preserve">742547, 7850930</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J14">
-        <v>232</v>
+        <v>60</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rude Havvej 21B</t>
+          <t xml:space="preserve">Rude Havvej 21C</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1101,16 +1101,16 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">742547, 7850930</t>
+          <t xml:space="preserve">742560, 7850930</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J15">
-        <v>60</v>
+        <v>188</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rude Havvej 21C</t>
+          <t xml:space="preserve">Skolegade 15B</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1176,16 +1176,16 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">742560, 7850930</t>
+          <t xml:space="preserve">100937944</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J16">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 15B</t>
+          <t xml:space="preserve">Skolegade 65</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1251,16 +1251,16 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">100937944</t>
+          <t xml:space="preserve">8567114, 100197236</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J17">
-        <v>185</v>
+        <v>2273</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 65</t>
+          <t xml:space="preserve">Skolegade 65A</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1331,11 +1331,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J18">
-        <v>2273</v>
+        <v>96</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 65A</t>
+          <t xml:space="preserve">Stenslund 7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1401,16 +1401,16 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8567114, 100197236</t>
+          <t xml:space="preserve">8097328</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J19">
-        <v>96</v>
+        <v>312</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1481,11 +1481,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J20">
-        <v>312</v>
+        <v>146</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1556,11 +1556,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J21">
-        <v>146</v>
+        <v>251</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 7</t>
+          <t xml:space="preserve">Strandgade 13A</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1626,16 +1626,16 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097328</t>
+          <t xml:space="preserve">742565, 9689940</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J22">
-        <v>251</v>
+        <v>151</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1706,11 +1706,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="J23">
-        <v>151</v>
+        <v>96</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgade 13A</t>
+          <t xml:space="preserve">Strandgade 5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1776,16 +1776,16 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">742565, 9689940</t>
+          <t xml:space="preserve">742510, 4194131</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J24">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1841,26 +1841,26 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgade 5</t>
+          <t xml:space="preserve">Tunø Hovedgade 10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8799</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">742510, 4194131</t>
+          <t xml:space="preserve">4248229</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J25">
-        <v>60</v>
+        <v>421</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tunø Hovedgade 10</t>
+          <t xml:space="preserve">Tunø Hovedgade 1D</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1926,16 +1926,16 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4248229</t>
+          <t xml:space="preserve">742602, 8567353</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J26">
-        <v>421</v>
+        <v>74</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1991,26 +1991,26 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tunø Hovedgade 1D</t>
+          <t xml:space="preserve">Vitavej 60</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8799</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">742602, 8567353</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J27">
-        <v>74</v>
+        <v>629</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Holsteinsgade 43A</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2076,35 +2076,35 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4199447</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J28">
-        <v>994</v>
+        <v>759</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026991</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Ålborg)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-19</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Rosensgade 84</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2151,35 +2151,35 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4199015</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J29">
-        <v>2372</v>
+        <v>132</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200033944</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Ålborg)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 60</t>
+          <t xml:space="preserve">Egholmvej 2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2226,35 +2226,35 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4197672</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J30">
-        <v>629</v>
+        <v>512</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311203242</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holsteinsgade 43A</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2301,30 +2301,30 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199447</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J31">
-        <v>759</v>
+        <v>276</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026991</t>
+          <t xml:space="preserve">311203232</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Ålborg)</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-19</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosensgade 84</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,30 +2376,30 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199015</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J32">
-        <v>132</v>
+        <v>282</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033944</t>
+          <t xml:space="preserve">311203232</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Ålborg)</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-13</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aahavevej 10</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2451,20 +2451,20 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197460</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J33">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203234</t>
+          <t xml:space="preserve">311203232</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aahavevej 10</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2526,20 +2526,20 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197460</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J34">
-        <v>153</v>
+        <v>499</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203234</t>
+          <t xml:space="preserve">311203232</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 2</t>
+          <t xml:space="preserve">Bronzealdervej 16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,20 +2601,20 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197672</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J35">
-        <v>512</v>
+        <v>270</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203242</t>
+          <t xml:space="preserve">311208182</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Saloparken 2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">7255382</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2685,11 +2685,11 @@
         </is>
       </c>
       <c r="J36">
-        <v>276</v>
+        <v>555</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311208186</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Saloparken 2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,20 +2751,20 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">7255382</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J37">
-        <v>282</v>
+        <v>141</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311208187</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Torvald Køhlsvej 50</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,20 +2826,20 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">9665232</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J38">
-        <v>294</v>
+        <v>398</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311208185</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Skolegade 15A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,20 +2901,20 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">4193708</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J39">
-        <v>499</v>
+        <v>398</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311218214</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 16</t>
+          <t xml:space="preserve">Venneslaparken 1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,20 +2976,20 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">7956622</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J40">
-        <v>270</v>
+        <v>480</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208182</t>
+          <t xml:space="preserve">311218471</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saloparken 2</t>
+          <t xml:space="preserve">Landevejen 30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255382</t>
+          <t xml:space="preserve">4194779</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3060,11 +3060,11 @@
         </is>
       </c>
       <c r="J41">
-        <v>555</v>
+        <v>275</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208186</t>
+          <t xml:space="preserve">311221278</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,30 +3116,30 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saloparken 2</t>
+          <t xml:space="preserve">Landevejen 30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255382</t>
+          <t xml:space="preserve">4194779</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J42">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208187</t>
+          <t xml:space="preserve">311221278</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvald Køhlsvej 50</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9665232</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,11 +3210,11 @@
         </is>
       </c>
       <c r="J43">
-        <v>398</v>
+        <v>894</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208185</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gylling Skolegade 12</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,20 +3276,20 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193329</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J44">
-        <v>442</v>
+        <v>121</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211745</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 15A</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,20 +3351,20 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193708</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J45">
-        <v>398</v>
+        <v>329</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218214</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venneslaparken 1</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,20 +3426,20 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7956622</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J46">
-        <v>480</v>
+        <v>428</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218471</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,30 +3491,30 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landevejen 30</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194779</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J47">
-        <v>275</v>
+        <v>160</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221278</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3566,30 +3566,30 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landevejen 30</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194779</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J48">
-        <v>245</v>
+        <v>1621</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221278</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Østermarksvej 25A</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100049247</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,21 +3660,21 @@
         </is>
       </c>
       <c r="J49">
-        <v>894</v>
+        <v>620</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311224995</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Bornak Arkitekter</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Nølevvej 4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,20 +3726,20 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">7349419</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J50">
-        <v>121</v>
+        <v>11918</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311230441</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Havrevænget 9A</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,20 +3801,20 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">4203491</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J51">
-        <v>329</v>
+        <v>132</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311247844</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Mejerivej 14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,20 +3876,20 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">4196620</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J52">
-        <v>428</v>
+        <v>887</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311253199</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Bronzealdervej 10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,20 +3951,20 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J53">
-        <v>160</v>
+        <v>787</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Bronzealdervej 12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J54">
-        <v>1621</v>
+        <v>787</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 1</t>
+          <t xml:space="preserve">Bronzealdervej 14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,20 +4101,20 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193843</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J55">
-        <v>3079</v>
+        <v>787</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221268</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 1</t>
+          <t xml:space="preserve">Bronzealdervej 2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4176,20 +4176,20 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193843</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J56">
-        <v>695</v>
+        <v>787</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221268</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 25A</t>
+          <t xml:space="preserve">Bronzealdervej 4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,30 +4251,30 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">100049247</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J57">
-        <v>620</v>
+        <v>787</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224995</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bornak Arkitekter</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gylling Skolegade 13</t>
+          <t xml:space="preserve">Bronzealdervej 6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,20 +4326,20 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193434</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J58">
-        <v>2202</v>
+        <v>787</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230442</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gylling Skolegade 13</t>
+          <t xml:space="preserve">Bronzealdervej 8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,20 +4401,20 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193434</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J59">
-        <v>176</v>
+        <v>324</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230442</t>
+          <t xml:space="preserve">311258869</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nølevvej 4</t>
+          <t xml:space="preserve">Rådhusgade 38</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">7349419</t>
+          <t xml:space="preserve">4196668</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4485,11 +4485,11 @@
         </is>
       </c>
       <c r="J60">
-        <v>11918</v>
+        <v>1377</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230441</t>
+          <t xml:space="preserve">311259724</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Rådhusgade 43</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4196792</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="J61">
-        <v>994</v>
+        <v>1063</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242492</t>
+          <t xml:space="preserve">311259573</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-24</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Rådhusgade 43</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4196792</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,11 +4635,11 @@
         </is>
       </c>
       <c r="J62">
-        <v>1212</v>
+        <v>1468</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242492</t>
+          <t xml:space="preserve">311259573</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-24</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Aaholmsgade 3A</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,20 +4701,20 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J63">
-        <v>1546</v>
+        <v>301</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242492</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-24</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havrevænget 9A</t>
+          <t xml:space="preserve">Aaholmsgade 3E</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,20 +4776,20 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4203491</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J64">
-        <v>132</v>
+        <v>310</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247844</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-17</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerivej 14</t>
+          <t xml:space="preserve">Aaholmsgade 3K</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,20 +4851,20 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196620</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J65">
-        <v>887</v>
+        <v>188</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253199</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-12</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 10</t>
+          <t xml:space="preserve">Aaholmsgade 3M</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,20 +4926,20 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J66">
-        <v>787</v>
+        <v>188</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 12</t>
+          <t xml:space="preserve">Ålykkecentret 5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,20 +5001,20 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J67">
-        <v>787</v>
+        <v>3261</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311270273</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 14</t>
+          <t xml:space="preserve">Stenslund 2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,20 +5076,20 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">369803</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J68">
-        <v>787</v>
+        <v>545</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311271441</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-07</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 2</t>
+          <t xml:space="preserve">Bisgaardsvej 54</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4197802</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5160,11 +5160,11 @@
         </is>
       </c>
       <c r="J69">
-        <v>787</v>
+        <v>145</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311274595</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-22</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 4</t>
+          <t xml:space="preserve">Stenslund 7</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,20 +5226,20 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">8097328</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J70">
-        <v>787</v>
+        <v>556</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311275612</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-28</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 6</t>
+          <t xml:space="preserve">Banegårdsgade 5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,20 +5301,20 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">8297681</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>787</v>
+        <v>700</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311275892</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 8</t>
+          <t xml:space="preserve">Rosensgade 10A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,20 +5376,20 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4197085</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J72">
-        <v>324</v>
+        <v>505</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258869</t>
+          <t xml:space="preserve">311276014</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 38</t>
+          <t xml:space="preserve">Rådhusgade 3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196668</t>
+          <t xml:space="preserve">4197028</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5460,11 +5460,11 @@
         </is>
       </c>
       <c r="J73">
-        <v>1377</v>
+        <v>6516</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259724</t>
+          <t xml:space="preserve">311275868</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 43</t>
+          <t xml:space="preserve">Stampmøllevej 57</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196792</t>
+          <t xml:space="preserve">8179547</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5535,11 +5535,11 @@
         </is>
       </c>
       <c r="J74">
-        <v>1063</v>
+        <v>105</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259573</t>
+          <t xml:space="preserve">311276002</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 43</t>
+          <t xml:space="preserve">Stampmøllevej 57</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196792</t>
+          <t xml:space="preserve">8179547</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5610,11 +5610,11 @@
         </is>
       </c>
       <c r="J75">
-        <v>1468</v>
+        <v>110</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259573</t>
+          <t xml:space="preserve">311276001</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3A</t>
+          <t xml:space="preserve">Bisgaardsvej 42</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,20 +5676,20 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">4198692</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76">
-        <v>301</v>
+        <v>170</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311276471</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2027-10-03</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3E</t>
+          <t xml:space="preserve">Holsteinsgade 43</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,30 +5751,30 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">4199447</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J77">
-        <v>310</v>
+        <v>8417</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311287701</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3K</t>
+          <t xml:space="preserve">Stenslund 6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,30 +5826,30 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">8331220</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J78">
-        <v>188</v>
+        <v>719</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311447305</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3M</t>
+          <t xml:space="preserve">Præstevænget 28</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,30 +5901,30 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J79">
-        <v>188</v>
+        <v>1313</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311555233</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålykkecentret 5</t>
+          <t xml:space="preserve">Vitaparkvej 17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,20 +5976,20 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J80">
-        <v>3261</v>
+        <v>394</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270273</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 2</t>
+          <t xml:space="preserve">Vitaparkvej 19</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,20 +6051,20 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">369803</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J81">
-        <v>545</v>
+        <v>1496</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271441</t>
+          <t xml:space="preserve">311555236</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-07</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bisgaardsvej 54</t>
+          <t xml:space="preserve">Vitaparkvej 6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,30 +6126,30 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197802</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J82">
-        <v>145</v>
+        <v>801</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311274595</t>
+          <t xml:space="preserve">311555234</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-22</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 7</t>
+          <t xml:space="preserve">Vitaparkvej 9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,20 +6201,20 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097328</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J83">
-        <v>556</v>
+        <v>1592</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275612</t>
+          <t xml:space="preserve">311555235</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-28</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdsgade 5</t>
+          <t xml:space="preserve">Vitaparkvej 9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6276,20 +6276,20 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8297681</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J84">
-        <v>700</v>
+        <v>3377</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275892</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosensgade 10A</t>
+          <t xml:space="preserve">Vitavej 63</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,20 +6351,20 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197085</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J85">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276014</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 3</t>
+          <t xml:space="preserve">Vitavej 71</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6426,20 +6426,20 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197028</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J86">
-        <v>6516</v>
+        <v>2608</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275868</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stampmøllevej 57</t>
+          <t xml:space="preserve">Tofts Vænge 1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8179547</t>
+          <t xml:space="preserve">100439978</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="J87">
-        <v>105</v>
+        <v>1105</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276002</t>
+          <t xml:space="preserve">311654677</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stampmøllevej 57</t>
+          <t xml:space="preserve">Vitaparkvej 1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6576,30 +6576,30 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8179547</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J88">
-        <v>110</v>
+        <v>5018</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276001</t>
+          <t xml:space="preserve">311663627</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2033-03-02</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bisgaardsvej 42</t>
+          <t xml:space="preserve">Skolevænget 3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,30 +6651,30 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198692</t>
+          <t xml:space="preserve">4193843</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J89">
-        <v>170</v>
+        <v>1056</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276471</t>
+          <t xml:space="preserve">311872142</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-03</t>
+          <t xml:space="preserve">2035-12-08</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holsteinsgade 43</t>
+          <t xml:space="preserve">Højmarkvej 10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199447</t>
+          <t xml:space="preserve">4197393</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6735,21 +6735,21 @@
         </is>
       </c>
       <c r="J90">
-        <v>8417</v>
+        <v>898</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287701</t>
+          <t xml:space="preserve">311915775</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 6</t>
+          <t xml:space="preserve">Lundevej 35A</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8331220</t>
+          <t xml:space="preserve">10081243</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6810,21 +6810,21 @@
         </is>
       </c>
       <c r="J91">
-        <v>719</v>
+        <v>850</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311447305</t>
+          <t xml:space="preserve">311915753</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-01</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstevænget 28</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,30 +6876,30 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">500006, 4198718</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J92">
-        <v>1313</v>
+        <v>1568</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555233</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 17</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,30 +6951,30 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">500006, 4198718</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J93">
-        <v>394</v>
+        <v>1560</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 19</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,30 +7026,30 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">500006, 500007, 4198718</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J94">
-        <v>1496</v>
+        <v>3017</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555236</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 6</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,30 +7101,30 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">500007, 4198718</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J95">
-        <v>801</v>
+        <v>332</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555234</t>
+          <t xml:space="preserve">311915756</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 9</t>
+          <t xml:space="preserve">Østermarksvej 21</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,30 +7176,30 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4198344</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J96">
-        <v>1592</v>
+        <v>569</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555235</t>
+          <t xml:space="preserve">311915750</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 9</t>
+          <t xml:space="preserve">Østermarksvej 21B</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7251,30 +7251,30 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4198348</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J97">
-        <v>3377</v>
+        <v>555</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311915749</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 63</t>
+          <t xml:space="preserve">Havrevænget 15</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7326,30 +7326,30 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">8037533</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J98">
-        <v>500</v>
+        <v>327</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311924130</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,40 +7391,40 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 71</t>
+          <t xml:space="preserve">Solhøjvej 12</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4195321</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J99">
-        <v>2608</v>
+        <v>371</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311924150</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tofts Vænge 1</t>
+          <t xml:space="preserve">Skolevænget 1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">100439978</t>
+          <t xml:space="preserve">4193843</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7485,21 +7485,21 @@
         </is>
       </c>
       <c r="J100">
-        <v>1105</v>
+        <v>3079</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654677</t>
+          <t xml:space="preserve">311926891</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2036-09-19</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 1</t>
+          <t xml:space="preserve">Skolevænget 1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,30 +7551,30 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4193843</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J101">
-        <v>5018</v>
+        <v>695</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311663627</t>
+          <t xml:space="preserve">311926891</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-02</t>
+          <t xml:space="preserve">2036-09-19</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 3</t>
+          <t xml:space="preserve">Gylling Skolegade 13</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7626,30 +7626,30 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193843</t>
+          <t xml:space="preserve">4193434</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J102">
-        <v>1056</v>
+        <v>2202</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872142</t>
+          <t xml:space="preserve">311928512</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-08</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarkvej 10</t>
+          <t xml:space="preserve">Gylling Skolegade 13</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,20 +7701,20 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197393</t>
+          <t xml:space="preserve">4193434</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J103">
-        <v>898</v>
+        <v>176</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915775</t>
+          <t xml:space="preserve">311928512</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 35A</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">10081243</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,11 +7785,11 @@
         </is>
       </c>
       <c r="J104">
-        <v>850</v>
+        <v>994</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915753</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,20 +7851,20 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 4198718</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J105">
-        <v>1568</v>
+        <v>1212</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,20 +7926,20 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 4198718</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J106">
-        <v>1560</v>
+        <v>994</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,20 +8001,20 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 500007, 4198718</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J107">
-        <v>3017</v>
+        <v>1546</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,20 +8076,20 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">500007, 4198718</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J108">
-        <v>332</v>
+        <v>2372</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915756</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 21</t>
+          <t xml:space="preserve">Alrøvej 357</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198344</t>
+          <t xml:space="preserve">4191418</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8160,11 +8160,11 @@
         </is>
       </c>
       <c r="J109">
-        <v>569</v>
+        <v>417</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915750</t>
+          <t xml:space="preserve">311929017</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 21B</t>
+          <t xml:space="preserve">Gylling Skolegade 12</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198348</t>
+          <t xml:space="preserve">4193329</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J110">
-        <v>555</v>
+        <v>442</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915749</t>
+          <t xml:space="preserve">311929154</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havrevænget 15</t>
+          <t xml:space="preserve">Aahavevej 10</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8037533</t>
+          <t xml:space="preserve">4197460</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924130</t>
+          <t xml:space="preserve">311929294</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-07</t>
+          <t xml:space="preserve">2036-10-01</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,30 +8366,30 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solhøjvej 12</t>
+          <t xml:space="preserve">Aahavevej 10</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4195321</t>
+          <t xml:space="preserve">4197460</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J112">
-        <v>371</v>
+        <v>153</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924150</t>
+          <t xml:space="preserve">311929294</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-07</t>
+          <t xml:space="preserve">2036-10-01</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">

--- a/public/exports-from-60/32264328.xlsx
+++ b/public/exports-from-60/32264328.xlsx
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tunø Hovedgade 10</t>
+          <t xml:space="preserve">Tunø Hovedgade 1D</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4248229</t>
+          <t xml:space="preserve">742602, 8567353</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J25">
-        <v>421</v>
+        <v>74</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tunø Hovedgade 1D</t>
+          <t xml:space="preserve">Vitavej 60</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">8799</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">742602, 8567353</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J26">
-        <v>74</v>
+        <v>629</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 60</t>
+          <t xml:space="preserve">Holsteinsgade 43A</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2001,35 +2001,35 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4199447</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J27">
-        <v>629</v>
+        <v>759</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026991</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Ålborg)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-19</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holsteinsgade 43A</t>
+          <t xml:space="preserve">Rosensgade 84</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2076,20 +2076,20 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199447</t>
+          <t xml:space="preserve">4199015</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J28">
-        <v>759</v>
+        <v>132</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026991</t>
+          <t xml:space="preserve">200033944</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-19</t>
+          <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosensgade 84</t>
+          <t xml:space="preserve">Egholmvej 2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199015</t>
+          <t xml:space="preserve">4197672</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="J29">
-        <v>132</v>
+        <v>512</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033944</t>
+          <t xml:space="preserve">311203242</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Ålborg)</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-13</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 2</t>
+          <t xml:space="preserve">Bronzealdervej 16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2226,20 +2226,20 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197672</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J30">
-        <v>512</v>
+        <v>270</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203242</t>
+          <t xml:space="preserve">311208182</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Saloparken 2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">7255382</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2310,11 +2310,11 @@
         </is>
       </c>
       <c r="J31">
-        <v>276</v>
+        <v>555</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311208186</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2324,17 +2324,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Saloparken 2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,20 +2376,20 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">7255382</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J32">
-        <v>282</v>
+        <v>141</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311208187</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2399,17 +2399,17 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Skolegade 15A</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2451,20 +2451,20 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">4193708</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J33">
-        <v>294</v>
+        <v>398</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311218214</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2474,17 +2474,17 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2516,30 +2516,30 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Landevejen 30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">4194779</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J34">
-        <v>499</v>
+        <v>275</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311221278</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2549,17 +2549,17 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2591,30 +2591,30 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 16</t>
+          <t xml:space="preserve">Landevejen 30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">4194779</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J35">
-        <v>270</v>
+        <v>245</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208182</t>
+          <t xml:space="preserve">311221278</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saloparken 2</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255382</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2685,11 +2685,11 @@
         </is>
       </c>
       <c r="J36">
-        <v>555</v>
+        <v>894</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208186</t>
+          <t xml:space="preserve">311221240</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saloparken 2</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,20 +2751,20 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255382</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J37">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208187</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvald Køhlsvej 50</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,20 +2826,20 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">9665232</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J38">
-        <v>398</v>
+        <v>329</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208185</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 15A</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,20 +2901,20 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193708</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J39">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218214</t>
+          <t xml:space="preserve">311221240</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venneslaparken 1</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,20 +2976,20 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">7956622</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J40">
-        <v>480</v>
+        <v>160</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218471</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,30 +3041,30 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landevejen 30</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194779</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J41">
-        <v>275</v>
+        <v>1621</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221278</t>
+          <t xml:space="preserve">311221240</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3116,40 +3116,40 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landevejen 30</t>
+          <t xml:space="preserve">Østermarksvej 25A</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194779</t>
+          <t xml:space="preserve">100049247</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J42">
-        <v>245</v>
+        <v>620</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221278</t>
+          <t xml:space="preserve">311224995</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Bornak Arkitekter</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Nølevvej 4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">7349419</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,11 +3210,11 @@
         </is>
       </c>
       <c r="J43">
-        <v>894</v>
+        <v>11918</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311230441</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Havrevænget 9A</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,20 +3276,20 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">4203491</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J44">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311247844</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Bronzealdervej 10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,20 +3351,20 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J45">
-        <v>329</v>
+        <v>787</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Bronzealdervej 12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,20 +3426,20 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J46">
-        <v>428</v>
+        <v>787</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Bronzealdervej 14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,20 +3501,20 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J47">
-        <v>160</v>
+        <v>787</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Bronzealdervej 2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,20 +3576,20 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J48">
-        <v>1621</v>
+        <v>787</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 25A</t>
+          <t xml:space="preserve">Bronzealdervej 4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3651,30 +3651,30 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">100049247</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J49">
-        <v>620</v>
+        <v>787</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224995</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bornak Arkitekter</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nølevvej 4</t>
+          <t xml:space="preserve">Bronzealdervej 6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,20 +3726,20 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7349419</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J50">
-        <v>11918</v>
+        <v>787</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230441</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havrevænget 9A</t>
+          <t xml:space="preserve">Bronzealdervej 8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,20 +3801,20 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4203491</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J51">
-        <v>132</v>
+        <v>324</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247844</t>
+          <t xml:space="preserve">311258869</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-17</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerivej 14</t>
+          <t xml:space="preserve">Rådhusgade 38</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196620</t>
+          <t xml:space="preserve">4196668</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3885,11 +3885,11 @@
         </is>
       </c>
       <c r="J52">
-        <v>887</v>
+        <v>1377</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253199</t>
+          <t xml:space="preserve">311259724</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-12</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 10</t>
+          <t xml:space="preserve">Rådhusgade 43</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,20 +3951,20 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196792</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J53">
-        <v>787</v>
+        <v>1063</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311259573</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 12</t>
+          <t xml:space="preserve">Rådhusgade 43</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196792</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J54">
-        <v>787</v>
+        <v>1468</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311259573</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 14</t>
+          <t xml:space="preserve">Aaholmsgade 3A</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,20 +4101,20 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J55">
-        <v>787</v>
+        <v>301</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 2</t>
+          <t xml:space="preserve">Aaholmsgade 3E</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4176,20 +4176,20 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J56">
-        <v>787</v>
+        <v>310</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 4</t>
+          <t xml:space="preserve">Aaholmsgade 3K</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,20 +4251,20 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J57">
-        <v>787</v>
+        <v>188</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 6</t>
+          <t xml:space="preserve">Aaholmsgade 3M</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,20 +4326,20 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J58">
-        <v>787</v>
+        <v>188</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 8</t>
+          <t xml:space="preserve">Ålykkecentret 5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,20 +4401,20 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J59">
-        <v>324</v>
+        <v>3261</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258869</t>
+          <t xml:space="preserve">311270273</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 38</t>
+          <t xml:space="preserve">Stenslund 2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196668</t>
+          <t xml:space="preserve">369803</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4485,11 +4485,11 @@
         </is>
       </c>
       <c r="J60">
-        <v>1377</v>
+        <v>545</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259724</t>
+          <t xml:space="preserve">311271441</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-09-07</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 43</t>
+          <t xml:space="preserve">Bisgaardsvej 54</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196792</t>
+          <t xml:space="preserve">4197802</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="J61">
-        <v>1063</v>
+        <v>145</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259573</t>
+          <t xml:space="preserve">311274595</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-09-22</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 43</t>
+          <t xml:space="preserve">Stenslund 7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,20 +4626,20 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196792</t>
+          <t xml:space="preserve">8097328</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J62">
-        <v>1468</v>
+        <v>556</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259573</t>
+          <t xml:space="preserve">311275612</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-09-28</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3A</t>
+          <t xml:space="preserve">Banegårdsgade 5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,20 +4701,20 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">8297681</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J63">
-        <v>301</v>
+        <v>700</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311275892</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3E</t>
+          <t xml:space="preserve">Rosensgade 10A</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,20 +4776,20 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">4197085</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J64">
-        <v>310</v>
+        <v>505</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311276014</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3K</t>
+          <t xml:space="preserve">Rådhusgade 3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,20 +4851,20 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">4197028</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J65">
-        <v>188</v>
+        <v>6516</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311275868</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3M</t>
+          <t xml:space="preserve">Stampmøllevej 57</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,20 +4926,20 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">8179547</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J66">
-        <v>188</v>
+        <v>105</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311276002</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålykkecentret 5</t>
+          <t xml:space="preserve">Stampmøllevej 57</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,20 +5001,20 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">8179547</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J67">
-        <v>3261</v>
+        <v>110</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270273</t>
+          <t xml:space="preserve">311276001</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 2</t>
+          <t xml:space="preserve">Bisgaardsvej 42</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">369803</t>
+          <t xml:space="preserve">4198692</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5085,11 +5085,11 @@
         </is>
       </c>
       <c r="J68">
-        <v>545</v>
+        <v>170</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271441</t>
+          <t xml:space="preserve">311276471</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-07</t>
+          <t xml:space="preserve">2027-10-03</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bisgaardsvej 54</t>
+          <t xml:space="preserve">Holsteinsgade 43</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197802</t>
+          <t xml:space="preserve">4199447</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5160,21 +5160,21 @@
         </is>
       </c>
       <c r="J69">
-        <v>145</v>
+        <v>8417</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311274595</t>
+          <t xml:space="preserve">311287701</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-22</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 7</t>
+          <t xml:space="preserve">Stenslund 6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097328</t>
+          <t xml:space="preserve">8331220</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="J70">
-        <v>556</v>
+        <v>719</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275612</t>
+          <t xml:space="preserve">311447305</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-28</t>
+          <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdsgade 5</t>
+          <t xml:space="preserve">Præstevænget 28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,30 +5301,30 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8297681</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J71">
-        <v>700</v>
+        <v>1313</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275892</t>
+          <t xml:space="preserve">311555233</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosensgade 10A</t>
+          <t xml:space="preserve">Vitaparkvej 17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,20 +5376,20 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197085</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J72">
-        <v>505</v>
+        <v>394</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276014</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 3</t>
+          <t xml:space="preserve">Vitaparkvej 19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,20 +5451,20 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197028</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J73">
-        <v>6516</v>
+        <v>1496</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275868</t>
+          <t xml:space="preserve">311555236</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stampmøllevej 57</t>
+          <t xml:space="preserve">Vitaparkvej 6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5526,30 +5526,30 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8179547</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J74">
-        <v>105</v>
+        <v>801</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276002</t>
+          <t xml:space="preserve">311555234</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stampmøllevej 57</t>
+          <t xml:space="preserve">Vitaparkvej 9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8179547</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J75">
-        <v>110</v>
+        <v>1592</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276001</t>
+          <t xml:space="preserve">311555235</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bisgaardsvej 42</t>
+          <t xml:space="preserve">Vitaparkvej 9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,20 +5676,20 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198692</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J76">
-        <v>170</v>
+        <v>3377</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276471</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-03</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holsteinsgade 43</t>
+          <t xml:space="preserve">Vitavej 63</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,30 +5751,30 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199447</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J77">
-        <v>8417</v>
+        <v>500</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287701</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 6</t>
+          <t xml:space="preserve">Vitavej 71</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,30 +5826,30 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8331220</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J78">
-        <v>719</v>
+        <v>2608</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311447305</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-01</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstevænget 28</t>
+          <t xml:space="preserve">Tofts Vænge 1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,30 +5901,30 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">100439978</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J79">
-        <v>1313</v>
+        <v>1105</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555233</t>
+          <t xml:space="preserve">311654677</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 17</t>
+          <t xml:space="preserve">Vitaparkvej 1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J80">
-        <v>394</v>
+        <v>5018</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311663627</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2033-03-02</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 19</t>
+          <t xml:space="preserve">Skolevænget 3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,30 +6051,30 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4193843</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J81">
-        <v>1496</v>
+        <v>1056</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555236</t>
+          <t xml:space="preserve">311872142</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2035-12-08</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 6</t>
+          <t xml:space="preserve">Højmarkvej 10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,30 +6126,30 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4197393</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J82">
-        <v>801</v>
+        <v>898</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555234</t>
+          <t xml:space="preserve">311915775</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 9</t>
+          <t xml:space="preserve">Lundevej 35A</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,30 +6201,30 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">10081243</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J83">
-        <v>1592</v>
+        <v>850</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555235</t>
+          <t xml:space="preserve">311915753</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 9</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6276,30 +6276,30 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">500006, 4198718</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J84">
-        <v>3377</v>
+        <v>1568</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 63</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,30 +6351,30 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">500006, 4198718</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J85">
-        <v>500</v>
+        <v>1560</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 71</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6426,30 +6426,30 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">500006, 500007, 4198718</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J86">
-        <v>2608</v>
+        <v>3017</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tofts Vænge 1</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,30 +6501,30 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">100439978</t>
+          <t xml:space="preserve">500007, 4198718</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J87">
-        <v>1105</v>
+        <v>332</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654677</t>
+          <t xml:space="preserve">311915756</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 1</t>
+          <t xml:space="preserve">Østermarksvej 21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4198344</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6585,21 +6585,21 @@
         </is>
       </c>
       <c r="J88">
-        <v>5018</v>
+        <v>569</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311663627</t>
+          <t xml:space="preserve">311915750</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-02</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 3</t>
+          <t xml:space="preserve">Østermarksvej 21B</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,30 +6651,30 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193843</t>
+          <t xml:space="preserve">4198348</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J89">
-        <v>1056</v>
+        <v>555</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872142</t>
+          <t xml:space="preserve">311915749</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-08</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarkvej 10</t>
+          <t xml:space="preserve">Havrevænget 15</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197393</t>
+          <t xml:space="preserve">8037533</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6735,11 +6735,11 @@
         </is>
       </c>
       <c r="J90">
-        <v>898</v>
+        <v>327</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915775</t>
+          <t xml:space="preserve">311924130</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,30 +6791,30 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 35A</t>
+          <t xml:space="preserve">Solhøjvej 12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">10081243</t>
+          <t xml:space="preserve">4195321</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J91">
-        <v>850</v>
+        <v>371</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915753</t>
+          <t xml:space="preserve">311924150</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Skolevænget 1</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,20 +6876,20 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 4198718</t>
+          <t xml:space="preserve">4193843</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J92">
-        <v>1568</v>
+        <v>3079</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311926891</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-19</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Skolevænget 1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,20 +6951,20 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 4198718</t>
+          <t xml:space="preserve">4193843</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J93">
-        <v>1560</v>
+        <v>695</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311926891</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-19</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Gylling Skolegade 13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,20 +7026,20 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 500007, 4198718</t>
+          <t xml:space="preserve">4193434</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J94">
-        <v>3017</v>
+        <v>2202</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311928512</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Gylling Skolegade 13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,20 +7101,20 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">500007, 4198718</t>
+          <t xml:space="preserve">4193434</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J95">
-        <v>332</v>
+        <v>176</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915756</t>
+          <t xml:space="preserve">311928512</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 21</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198344</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7185,11 +7185,11 @@
         </is>
       </c>
       <c r="J96">
-        <v>569</v>
+        <v>994</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915750</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 21B</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7251,20 +7251,20 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198348</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J97">
-        <v>555</v>
+        <v>1212</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915749</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havrevænget 15</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7326,20 +7326,20 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8037533</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J98">
-        <v>327</v>
+        <v>994</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924130</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-07</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,30 +7391,30 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solhøjvej 12</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4195321</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J99">
-        <v>371</v>
+        <v>1546</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924150</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-07</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 1</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,20 +7476,20 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193843</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J100">
-        <v>3079</v>
+        <v>2372</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926891</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-19</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 1</t>
+          <t xml:space="preserve">Alrøvej 357</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,20 +7551,20 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193843</t>
+          <t xml:space="preserve">4191418</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J101">
-        <v>695</v>
+        <v>417</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926891</t>
+          <t xml:space="preserve">311929017</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-19</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gylling Skolegade 13</t>
+          <t xml:space="preserve">Gylling Skolegade 12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193434</t>
+          <t xml:space="preserve">4193329</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7635,11 +7635,11 @@
         </is>
       </c>
       <c r="J102">
-        <v>2202</v>
+        <v>442</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928512</t>
+          <t xml:space="preserve">311929154</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gylling Skolegade 13</t>
+          <t xml:space="preserve">Aahavevej 10</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,20 +7701,20 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193434</t>
+          <t xml:space="preserve">4197460</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J103">
-        <v>176</v>
+        <v>253</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928512</t>
+          <t xml:space="preserve">311929675</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-10-01</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Aahavevej 10</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,20 +7776,20 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4197460</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J104">
-        <v>994</v>
+        <v>153</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928518</t>
+          <t xml:space="preserve">311929675</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-10-01</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Venneslaparken 1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,20 +7851,20 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">7956622</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J105">
-        <v>1212</v>
+        <v>480</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928518</t>
+          <t xml:space="preserve">311929537</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Mejerivej 14</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,20 +7926,20 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4196620</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>994</v>
+        <v>887</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928518</t>
+          <t xml:space="preserve">311930179</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,20 +8001,20 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J107">
-        <v>1546</v>
+        <v>276</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928518</t>
+          <t xml:space="preserve">311930676</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-10-08</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,20 +8076,20 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J108">
-        <v>2372</v>
+        <v>282</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928518</t>
+          <t xml:space="preserve">311930676</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-10-08</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alrøvej 357</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,20 +8151,20 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4191418</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J109">
-        <v>417</v>
+        <v>294</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929017</t>
+          <t xml:space="preserve">311930676</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-30</t>
+          <t xml:space="preserve">2036-10-08</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gylling Skolegade 12</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,20 +8226,20 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193329</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J110">
-        <v>442</v>
+        <v>499</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929154</t>
+          <t xml:space="preserve">311930676</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-30</t>
+          <t xml:space="preserve">2036-10-08</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aahavevej 10</t>
+          <t xml:space="preserve">Torvald Køhlsvej 50</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197460</t>
+          <t xml:space="preserve">9665232</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>253</v>
+        <v>398</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929294</t>
+          <t xml:space="preserve">311930697</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-10-01</t>
+          <t xml:space="preserve">2036-10-08</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,30 +8366,30 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aahavevej 10</t>
+          <t xml:space="preserve">Tunø Hovedgade 10</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8799</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197460</t>
+          <t xml:space="preserve">4248229</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J112">
-        <v>153</v>
+        <v>421</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929294</t>
+          <t xml:space="preserve">311931066</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-10-01</t>
+          <t xml:space="preserve">2036-10-09</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
